--- a/光伏配储项目/电价数据/2026/清水河站.xlsx
+++ b/光伏配储项目/电价数据/2026/清水河站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.75574</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38461</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.84537</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5919500000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.72401</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1.10025</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.44222</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45981</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43194</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42662</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42456</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41258</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.40026</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39972</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38758</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.4044700000000001</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42759</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41627</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39438</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38757</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.42019</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39481</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42405</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.4171</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42724</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41488</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44693</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.5012799999999999</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.40051</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37402</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.12283</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.13505</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.35436</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.14113</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.07403</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.11384</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.53511</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.21135</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.3087</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.05093</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.77193</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.20379</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14784</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21929</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.22947</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.23472</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21868</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.68537</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.30505</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.42241</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.14902</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29072</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.29761</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.52549</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.6790900000000001</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.77024</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.95705</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7310800000000001</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.66155</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39448</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43129</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43647</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.65822</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.19614</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.80402</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.53258</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.38327</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.61307</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.77199</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.01542</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.07316</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.77818</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.32241</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.87107</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.7964600000000001</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7570399999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51758</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47951</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46891</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41572</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42537</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.70812</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.76848</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.87114</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.91583</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49423</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51466</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50254</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50278</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48505</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39933</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46717</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37804</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.3782</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.37873</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.3662</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.36794</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37398</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.87578</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.71909</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.81455</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.4561</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.43756</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37725</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38675</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42618</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5087</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.35469</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.39702</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.3033</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.33853</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.37426</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.50596</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.77715</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.99122</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.52162</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.88889</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.84512</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.49658</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.72353</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.31781</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.07623</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.02534</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.29472</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.3735</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.46987</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.54515</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.49791</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.52235</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.92074</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.62248</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.94653</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.31696</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.54135</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.17709</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.11732</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.58744</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.48961</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.645</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.42336</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.47453</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.03126</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.367</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.9020499999999999</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.44888</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.53745</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.3567</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.14135</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45018</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.78711</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.80784</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44898</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42811</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44361</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37563</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35469</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.3346</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.4867</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48716</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37807</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44762</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41409</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.3892</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38269</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36311</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42762</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44305</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37004</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39548</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36684</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36772</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36331</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35723</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38343</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39507</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47205</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44389</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43781</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39424</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.49995</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.67864</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.8947000000000001</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.81299</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.75081</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.24975</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.37763</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.36394</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.39138</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.40612</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.55414</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.49577</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.81853</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.39162</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.5913099999999999</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.7234299999999999</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.81192</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.52812</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.54699</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.79923</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.22467</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.68152</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.59802</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.4935</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.4459</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42527</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.39453</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.78154</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.5205299999999999</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.50424</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.57012</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.59537</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.54277</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.56262</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.26483</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6162799999999999</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.18373</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.50443</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5341699999999999</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.57511</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.9684299999999999</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.02859</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.40856</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.8499</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.82925</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.6695099999999999</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.91871</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6102000000000001</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.90125</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.5626</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.29966</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.86687</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.55949</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.48206</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.61576</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.51363</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45669</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39739</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34195</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5217000000000001</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49368</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44456</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38926</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40366</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36704</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38749</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38562</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36144</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44859</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36302</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35854</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33743</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35103</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38513</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38847</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37477</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.3439700000000001</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39328</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41592</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.52346</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35645</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.75339</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.63446</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.86871</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.19611</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.79762</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.9238</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>1.3969</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.6948</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.41919</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.25886</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>1.1698</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.00844</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>1.49537</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.9622200000000001</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.36224</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.45575</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.60424</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.42155</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.47988</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.40469</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39884</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.9429999999999999</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.82821</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.38318</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.45041</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.42787</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.4951</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45024</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46171</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39961</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.4741</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.51979</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.9254199999999999</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.44507</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.99102</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.88182</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50071</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.80532</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.75566</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.64671</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41591</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.5454199999999999</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.54159</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34154</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31398</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31754</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.7184400000000001</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.83988</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.36339</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33213</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31292</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31075</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.31011</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31468</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.44269</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.31252</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.3256</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.30473</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.19867</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.45369</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.42346</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.22031</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.15573</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.28672</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.38696</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.40234</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.27081</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.1892</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.5154</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.48825</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.05082</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.3776600000000001</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22411</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.44737</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.21039</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.06347999999999999</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.10273</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.00057</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.00261</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.04376</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26995</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29759</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29995</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.3336</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.37773</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.3833</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.37795</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35756</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.38961</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39257</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40135</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46136</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37102</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39056</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39236</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.48647</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35678</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35394</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34435</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36625</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.59054</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.38056</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.40593</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.38879</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.38397</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35171</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.30505</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.28854</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.27192</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.28576</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.31168</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.29695</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29235</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.29332</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.34614</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.30644</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10275</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04356</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04476</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.35751</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01531</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.21631</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05429999999999999</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.29033</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.2054</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.06658</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.3637</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04423</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.07045999999999999</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.0687</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34716</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33157</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31305</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.39562</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27071</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29732</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38681</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42757</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45536</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38673</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.2943</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78523</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142100000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8628899999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29622</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88751</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18709</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87787</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.18043</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33086</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03292</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53079</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79099</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.84838</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77298</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77755</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87387</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49315</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.3999</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44995</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.207</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62186</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45582</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44963</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41967</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.34719</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39854</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36287</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.40937</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.42675</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38708</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34604</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.38555</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44935</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.34709</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39294</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.38464</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5598200000000001</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.4123</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.58487</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8766499999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46655</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.39296</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5532</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.43465</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8191900000000001</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.57224</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.85323</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87498</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.4194</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.63122</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30298</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.29423</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.63405</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.5924700000000001</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>1.30412</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33436</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31716</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31955</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.30921</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30161</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29586</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.28858</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30077</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.30468</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.31121</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.34846</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33229</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.39118</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.42439</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.39313</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.37473</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.34711</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9140199999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.44484</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40773</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.39429</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.43844</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.36728</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.39086</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.37857</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.46346</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.3699</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.35634</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.30791</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.30945</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33163</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28825</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30074</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.18857</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33427</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.35798</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31077</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.2731</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19779</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.30521</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29876</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28154</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30924</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.30968</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.34837</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35671</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.30894</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.30238</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31088</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.31292</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31716</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.31009</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.29823</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29593</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30096</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.3088399999999999</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.30738</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28857</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25378</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.31307</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.32695</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27447</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.32979</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30218</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.36991</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.41356</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.12514</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42036</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44053</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.40126</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35187</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.38115</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.37894</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.53627</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.86736</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.44376</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.1398</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.6870299999999999</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.77735</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.63871</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.50876</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.40307</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44056</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49052</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43081</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.41724</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.40563</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.40493</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.40526</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.46437</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.40514</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.42572</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.39022</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.42632</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38438</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.40101</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.41913</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.38867</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.41647</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.40655</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.40517</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.40743</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.37875</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.39537</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39087</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.48696</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.28812</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.35676</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30586</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33444</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30451</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.30841</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.29938</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.52542</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.23097</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24838</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.30119</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15516</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27439</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27537</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.01041</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.25994</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25304</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30911</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28178</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.2954</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.30995</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.28928</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30478</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31123</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.32902</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38828</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.38494</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34428</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33327</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.32223</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.35477</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5438200000000001</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.43427</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.78915</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.43556</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.41804</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.3649</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.44128</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.37033</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.30815</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.3911</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.30235</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.30074</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.29545</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.29659</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.28846</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.29255</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.30897</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31154</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.30763</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.28386</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30092</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.31574</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.30311</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.24717</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.2902</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.25141</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.31857</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.29874</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.24204</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.2767</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.26472</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22921</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.23894</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.23439</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.26787</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28425</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.29457</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.30455</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.24203</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.29145</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.24941</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.29482</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.2674</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.45307</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.40445</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.42724</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.36457</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.34696</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.41876</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.3786</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.37207</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.37743</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.42279</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.41047</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.41085</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.43816</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38313</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39076</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38466</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.33533</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.49377</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38281</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.43727</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.40076</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.39404</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.3561</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.36524</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.36404</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.37544</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37366</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.3642</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.36633</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.3748</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.36418</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.34421</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.42081</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.36478</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.34836</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.33401</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35515</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29477</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31668</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.32702</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.30147</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.31326</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.30338</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.9288500000000001</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.84674</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.36364</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.3946</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.25191</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27851</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30131</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31774</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31353</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.2395</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.3036</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.52118</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.54008</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.42408</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.59099</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.5418999999999999</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.42114</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33453</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.84174</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.91474</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.37521</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.41073</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34215</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.40993</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.8693</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>1.10045</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.7644299999999999</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.13568</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.4283</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37818</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.43156</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.43061</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.42514</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.72038</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.47937</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.42201</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.36659</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.37059</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.34933</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.46322</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3646</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.47579</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.36664</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.33866</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.33172</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.37403</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.3692</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.36257</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.40838</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.70935</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.8217300000000001</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.81016</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.51132</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.74353</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.46884</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>1.14607</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.82547</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.80938</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.11228</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.78011</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.30738</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.17793</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.21294</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.73122</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.15136</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.39987</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>1.3313</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.6179</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.47598</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>1.29173</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.52467</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.68002</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.54516</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.6966</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.29816</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.60029</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.03022</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.76962</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.35831</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.77738</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.74411</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.8327899999999999</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.7598200000000001</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.75499</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.31807</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.88147</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.71745</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.8613999999999999</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.8433200000000001</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.11812</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.79051</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.66234</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.61372</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.5217000000000001</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.36849</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.50376</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.24105</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37004</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>1.54721</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.3123</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.91216</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.41357</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.3159</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.39748</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.36522</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.31593</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.38289</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.30182</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.30299</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31371</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.31314</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.30155</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.30637</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.31739</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.29848</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.37318</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.37185</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>1.07687</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.36494</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.49427</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.3430299999999999</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33197</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32685</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.27719</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.31782</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.30751</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31193</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.8681599999999999</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>1.21988</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.46164</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.1336</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.5302</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.35723</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.37025</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.3424700000000001</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.33968</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.8916799999999999</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.38261</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.8884099999999999</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.36581</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.36527</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.34847</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34344</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34321</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.34466</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34322</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.28214</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.35151</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.33886</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.31713</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30081</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32368</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36968</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.74726</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>1.31322</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.42047</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.54764</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.42508</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.38787</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.41601</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.49654</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.36537</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5892500000000001</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38762</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.42125</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.38845</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.44875</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.40852</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37099</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.50545</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.42622</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.37221</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.4064700000000001</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.62925</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37586</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65097</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.42924</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.69071</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.6223099999999999</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.89891</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.71751</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.33467</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40489</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37003</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35293</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35322</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35355</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.35266</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.36438</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37363</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34327</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32547</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>1.45352</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.47961</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.8725599999999999</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.5791499999999999</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.93344</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.47455</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.68192</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.3420899999999999</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.99918</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.39392</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.2995</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.29255</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.29283</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28576</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.30474</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34385</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.35408</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.7051000000000001</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.37217</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.43653</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.75559</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.57455</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.91634</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.78408</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.34994</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.7314700000000001</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.7094</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.97877</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.73911</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.97102</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.36449</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.41966</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.3954</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.42626</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.04096</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.99878</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.41911</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.9085700000000001</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.10323</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.92073</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.88554</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.79684</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.46804</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.38966</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.76516</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.39881</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.36698</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.36888</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.351</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.45634</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.52967</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.47614</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.61979</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.39674</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39689</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.38555</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.39055</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.38996</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.39619</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.38257</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.38839</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.39447</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.39266</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38169</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.37169</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.39478</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.3736</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.37673</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.37807</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.41566</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.41769</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.50573</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.46102</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.42194</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.45812</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.42043</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.5975199999999999</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.30474</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.96412</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.35198</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.3886</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.46829</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.42829</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.35677</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.89088</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.89219</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.91377</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.53439</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.8037799999999999</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.8350700000000001</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.82617</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.90552</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.15465</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.18666</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.51774</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.87906</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.88073</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.8709600000000001</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.86998</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.31469</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33434</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35247</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.35604</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.3718</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.36545</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.39365</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.41372</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.4593</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.42137</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.47333</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.47356</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.50673</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.6248899999999999</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.73353</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.8227899999999999</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.5907100000000001</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.71511</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.0892</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.40267</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.73576</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7652599999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6180399999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.66638</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.59491</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.00645</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.44927</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.44556</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.43871</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.39803</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5071100000000001</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.40642</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.41737</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.42801</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42831</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.41823</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.41935</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.40997</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.38188</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.41744</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.37546</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.38198</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.43943</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.37023</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.36492</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.29953</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.34464</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35368</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.36388</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.36843</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37335</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39555</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38176</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39312</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.38033</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.36978</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.8860399999999999</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.8557400000000001</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.8522000000000001</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.8724299999999999</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.86152</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>1.35433</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.87349</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.95257</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.9101</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.9626399999999999</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.40137</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.15306</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.21765</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30169</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29921</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.33736</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.35854</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.37956</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.8825</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.5421900000000001</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42505</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.4113</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.42559</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.40194</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.39406</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.35171</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.35515</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.37375</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.38126</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.32741</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.37142</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.36174</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35557</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.35326</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.33326</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.30029</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.46115</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="G135" t="n">
+        <v>1.52647</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.34666</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.31309</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.30109</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.28467</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.28206</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.31302</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.28282</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.26962</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.29577</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.30359</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.2994</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.30394</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.30848</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.26192</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.31301</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.26098</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.25591</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.29023</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.28352</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30805</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.25122</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.30761</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30362</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.18939</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28276</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.2451</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.27325</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.2618</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25806</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.09888</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.27552</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25713</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.03463</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28975</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28159</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.19419</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.39353</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30766</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.24895</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.26858</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.25847</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.24027</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.2763</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28494</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.27579</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36407</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.40917</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.44466</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.43515</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.37959</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.65873</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30324</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.33737</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.6605800000000001</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.42781</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.50107</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.37312</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.32878</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.31004</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.32465</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.30253</v>
+      </c>
+      <c r="C136" t="n">
+        <v>1.1279</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.27439</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.29511</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.30714</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.24344</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.28772</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.29511</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.29121</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.25287</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.24289</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.24557</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.24556</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.24228</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.24228</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.24425</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.28329</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.23898</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.24228</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.2426</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.2831</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.24304</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.24282</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.24979</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.16648</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.26707</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.21362</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01289</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.00023</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14588</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02126</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03957</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01536</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04286</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04075</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04859</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04824000000000001</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02923</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00021</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27446</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03824</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01888</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03614</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.2015</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26485</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28838</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27919</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.3085</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.24689</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.34087</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.33886</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.34477</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.3658</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.42093</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.36804</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.34896</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.34394</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.31368</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.33188</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.7369199999999999</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.63383</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.38704</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.43005</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.39437</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.41541</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.42455</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.36113</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.3031</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.26469</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.30424</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.28832</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.26297</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.2442</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.28016</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.26867</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.2987</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.26509</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.28928</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.30138</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.32456</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.43682</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.34182</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.26902</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.36882</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.68167</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.83999</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.87706</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.85082</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.38231</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.21708</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.29369</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.30732</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.29793</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.26601</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29946</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.25819</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.27108</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00257</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.27367</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31177</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.3141</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.29248</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06007</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.28642</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.29925</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.28931</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30278</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25521</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29233</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47123</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32312</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.39075</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.37181</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.36191</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.39238</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.50033</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.79213</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.74724</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.77125</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.34236</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.9817400000000001</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.7623300000000001</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.8352999999999999</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.79342</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.84033</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.83853</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.8428300000000001</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.9400299999999999</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.7536</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.78937</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.75662</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.39226</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.35581</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.37237</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.36406</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.36389</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.46691</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.61107</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.65859</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.57282</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.4937</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.46223</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.40289</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.39282</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.38097</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.37346</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.47634</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32231</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.31245</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.2849</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.36706</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.46259</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.47423</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.36772</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.38504</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32408</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.42535</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.37521</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.4516</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.36403</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.41467</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.39498</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.35397</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.38625</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.34632</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33514</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26714</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30957</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32361</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.34394</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31553</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34827</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34752</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35789</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.3533</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.40155</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.38957</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.37489</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.3737799999999999</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.43103</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.45476</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.7176399999999999</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.4069</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.59213</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.45986</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.38072</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.42089</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.41027</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.38979</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.47204</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.35322</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.35706</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33809</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.42048</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.4237</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.40814</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.3915</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.38387</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.37708</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.3416</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.40656</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.3664</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.55341</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.76401</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.5396599999999999</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.50351</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.5551799999999999</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.4472</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.36298</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.35694</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.35714</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.38794</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35141</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30556</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.60061</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.56728</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.59101</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.63714</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.47896</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34315</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.55688</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32791</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.5754400000000001</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.34719</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.34683</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.74699</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.89428</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47915</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.30711</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.35116</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>1.03462</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.4638</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.71269</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.55928</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.4573</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.45557</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.91242</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>1.2198</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>1.49197</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.6385</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.51913</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.42099</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.35646</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.36383</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.23517</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.35257</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.45419</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.38186</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.37806</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.36568</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.35693</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36335</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.33257</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.34071</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.37165</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.35286</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.38086</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39125</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36542</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43497</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37996</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.36242</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.37461</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>1.79075</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.45391</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.8438</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.49568</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.9452200000000001</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.5935199999999999</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.45586</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.7311</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33661</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.36907</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.36563</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.37192</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.5684199999999999</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.37598</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.39524</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.37386</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.37515</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.4183</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.41291</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.51225</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.15519</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.70756</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.9808300000000001</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.77811</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.63822</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.47562</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.2413</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.45265</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.34681</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.27079</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.82982</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>1.05756</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.97296</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.48617</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.3632</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.35696</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.30108</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.35778</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34322</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.3678</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34301</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.23263</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37564</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37562</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35326</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.33536</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.55987</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.79031</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>1.58784</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.8261799999999999</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.65779</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.7946299999999999</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.76419</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.8856000000000001</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.7906</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.81121</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.5807</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.48792</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.36207</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.57857</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.75227</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.46988</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.52078</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.36631</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.37152</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.85784</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.7233999999999999</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.87627</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.90266</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.72714</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.48378</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.9353899999999999</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.88388</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.9222400000000001</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.88675</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.59137</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.39937</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.5164299999999999</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.4065299999999999</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.36978</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.42265</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.6713</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.36075</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.36367</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34268</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.39856</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.23319</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.56231</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.6229</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.95699</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.44165</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37128</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36788</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.37107</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.3674</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.36352</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.36617</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36682</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.37046</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35715</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.34201</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.37506</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36445</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.7955599999999999</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.43104</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.17962</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.36789</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.67431</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.47253</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.99762</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.72049</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.34715</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32255</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.37539</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.46064</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42632</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.40368</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.38562</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.36272</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38231</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.45109</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.48092</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.6196799999999999</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5578099999999999</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.52685</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.45428</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38313</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.44681</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.06019</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.29963</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.98442</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.5401900000000001</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.9741000000000001</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>1.30509</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.14389</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.63517</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.35897</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.41515</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38541</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="F143" t="n">
+        <v>1.37149</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37657</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36778</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.36978</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.36832</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.36274</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>1.36556</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35734</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.35813</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>1.35543</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>1.34952</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31286</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17558</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30603</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31066</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14526</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19792</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14172</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.29105</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04456</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12129</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22579</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26543</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.15086</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14373</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28848</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1.19573</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>1.30407</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22606</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.26199</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15292</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30763</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.1527</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.29924</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19665</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14261</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.27957</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.63962</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>1.08059</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.49787</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.52081</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.53837</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38478</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>1.68613</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>1.08277</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.7038300000000001</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.5144299999999999</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.39875</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.77228</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.5646599999999999</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.39222</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.41733</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.5720499999999999</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.38862</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.54906</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40138</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.67638</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.5577799999999999</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.5515599999999999</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.61491</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38356</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38453</v>
       </c>
     </row>
   </sheetData>
